--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.98196</v>
+        <v>16.84209</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0411</v>
+        <v>16.39139</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44457</v>
+        <v>16.79752</v>
       </c>
       <c r="F2" t="n">
-        <v>42.72408</v>
+        <v>43.12979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05019</v>
+        <v>0.05061</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81056</v>
+        <v>1.79679</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.78377</v>
+        <v>16.89223</v>
       </c>
       <c r="D3" t="n">
-        <v>16.21814</v>
+        <v>16.59013</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58874</v>
+        <v>16.76425</v>
       </c>
       <c r="F3" t="n">
-        <v>42.02837</v>
+        <v>42.46915</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05007</v>
+        <v>0.05118</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82343</v>
+        <v>1.8052</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.56247</v>
+        <v>17.1385</v>
       </c>
       <c r="D4" t="n">
-        <v>16.32789</v>
+        <v>16.66796</v>
       </c>
       <c r="E4" t="n">
-        <v>16.82121</v>
+        <v>16.86119</v>
       </c>
       <c r="F4" t="n">
-        <v>42.43905</v>
+        <v>42.49709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05059</v>
+        <v>0.0505</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82528</v>
+        <v>1.82478</v>
       </c>
     </row>
   </sheetData>
